--- a/Results/Stand/Normal/FindPrincipalComponents_PipelinePCA_Stand/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Stand/Normal/FindPrincipalComponents_PipelinePCA_Stand/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,130 +677,130 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>94.66666666666667</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C2" t="n">
-        <v>95.55555555555557</v>
+        <v>92.22222222222223</v>
       </c>
       <c r="D2" t="n">
-        <v>94.66666666666666</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E2" t="n">
-        <v>97.33333333333334</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F2" t="n">
-        <v>94.6127946127946</v>
+        <v>90.52188552188551</v>
       </c>
       <c r="G2" t="n">
-        <v>94.66666666666666</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H2" t="n">
+        <v>5.333333333333332</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.444444444444446</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.333333333333332</v>
+      </c>
+      <c r="K2" t="n">
         <v>2.666666666666666</v>
       </c>
-      <c r="I2" t="n">
-        <v>2.222222222222219</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.666666666666671</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.333333333333333</v>
-      </c>
       <c r="L2" t="n">
-        <v>2.693602693602695</v>
+        <v>5.488215488215489</v>
       </c>
       <c r="M2" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="C3" t="n">
+        <v>92.06349206349206</v>
+      </c>
+      <c r="D3" t="n">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="E3" t="n">
         <v>94.66666666666667</v>
       </c>
-      <c r="C3" t="n">
-        <v>95.55555555555557</v>
-      </c>
-      <c r="D3" t="n">
-        <v>94.66666666666666</v>
-      </c>
-      <c r="E3" t="n">
-        <v>97.33333333333334</v>
-      </c>
       <c r="F3" t="n">
-        <v>94.6127946127946</v>
+        <v>88.97306397306399</v>
       </c>
       <c r="G3" t="n">
-        <v>94.66666666666666</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="I3" t="n">
-        <v>2.222222222222219</v>
+        <v>1.944039478399352</v>
       </c>
       <c r="J3" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710897</v>
       </c>
       <c r="K3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855457</v>
       </c>
       <c r="L3" t="n">
-        <v>2.693602693602695</v>
+        <v>3.505162089841244</v>
       </c>
       <c r="M3" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710897</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>94.66666666666667</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>95.55555555555557</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="D4" t="n">
-        <v>94.66666666666666</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E4" t="n">
-        <v>97.33333333333334</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>94.6127946127946</v>
+        <v>90.4040404040404</v>
       </c>
       <c r="G4" t="n">
-        <v>94.66666666666666</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="I4" t="n">
-        <v>2.222222222222219</v>
+        <v>1.944039478399352</v>
       </c>
       <c r="J4" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710897</v>
       </c>
       <c r="K4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855457</v>
       </c>
       <c r="L4" t="n">
-        <v>2.693602693602695</v>
+        <v>3.505162089841245</v>
       </c>
       <c r="M4" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>94.66666666666667</v>
@@ -841,89 +841,89 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>94.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>95.55555555555557</v>
+        <v>94.76190476190476</v>
       </c>
       <c r="D6" t="n">
-        <v>94.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>97.33333333333334</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="F6" t="n">
-        <v>94.6127946127946</v>
+        <v>93.18181818181819</v>
       </c>
       <c r="G6" t="n">
-        <v>94.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>2.666666666666666</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="I6" t="n">
-        <v>2.222222222222219</v>
+        <v>3.036686741223649</v>
       </c>
       <c r="J6" t="n">
-        <v>2.666666666666671</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="K6" t="n">
-        <v>1.333333333333333</v>
+        <v>2.108185106778923</v>
       </c>
       <c r="L6" t="n">
-        <v>2.693602693602695</v>
+        <v>4.393262070942723</v>
       </c>
       <c r="M6" t="n">
-        <v>2.666666666666671</v>
+        <v>4.216370213557838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>94.66666666666667</v>
+        <v>96.00000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D7" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G7" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="H7" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="I7" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J7" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K7" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L7" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M7" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>94.66666666666667</v>
@@ -964,54 +964,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>94.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>95.55555555555557</v>
+        <v>94.22222222222223</v>
       </c>
       <c r="D9" t="n">
-        <v>94.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>97.33333333333334</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>94.6127946127946</v>
+        <v>93.27946127946127</v>
       </c>
       <c r="G9" t="n">
-        <v>94.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>2.666666666666666</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="I9" t="n">
-        <v>2.222222222222219</v>
+        <v>3.874576838702822</v>
       </c>
       <c r="J9" t="n">
-        <v>2.666666666666671</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="K9" t="n">
-        <v>1.333333333333333</v>
+        <v>2.108185106778923</v>
       </c>
       <c r="L9" t="n">
-        <v>2.693602693602695</v>
+        <v>4.237697115206764</v>
       </c>
       <c r="M9" t="n">
-        <v>2.666666666666671</v>
+        <v>4.216370213557838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>95.55555555555557</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="D10" t="n">
         <v>94.66666666666666</v>
@@ -1020,80 +1020,80 @@
         <v>97.33333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>94.6127946127946</v>
+        <v>94.62626262626263</v>
       </c>
       <c r="G10" t="n">
         <v>94.66666666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2.666666666666666</v>
+        <v>4.988876515698587</v>
       </c>
       <c r="I10" t="n">
-        <v>2.222222222222219</v>
+        <v>4.521553322083512</v>
       </c>
       <c r="J10" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="K10" t="n">
-        <v>1.333333333333333</v>
+        <v>2.494438257849297</v>
       </c>
       <c r="L10" t="n">
-        <v>2.693602693602695</v>
+        <v>5.017698160896139</v>
       </c>
       <c r="M10" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>94.66666666666667</v>
+        <v>96.00000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>95.55555555555557</v>
+        <v>96.44444444444446</v>
       </c>
       <c r="D11" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>94.6127946127946</v>
+        <v>95.97306397306397</v>
       </c>
       <c r="G11" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.666666666666666</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="I11" t="n">
-        <v>2.222222222222219</v>
+        <v>4.838120234906054</v>
       </c>
       <c r="J11" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>1.333333333333333</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="L11" t="n">
-        <v>2.693602693602695</v>
+        <v>5.363652215794517</v>
       </c>
       <c r="M11" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="C12" t="n">
-        <v>95.55555555555557</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="D12" t="n">
         <v>94.66666666666666</v>
@@ -1102,121 +1102,121 @@
         <v>97.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>94.6127946127946</v>
+        <v>94.62626262626263</v>
       </c>
       <c r="G12" t="n">
         <v>94.66666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2.666666666666666</v>
+        <v>4.988876515698587</v>
       </c>
       <c r="I12" t="n">
-        <v>2.222222222222219</v>
+        <v>4.521553322083512</v>
       </c>
       <c r="J12" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="K12" t="n">
-        <v>1.333333333333333</v>
+        <v>2.494438257849297</v>
       </c>
       <c r="L12" t="n">
-        <v>2.693602693602695</v>
+        <v>5.017698160896139</v>
       </c>
       <c r="M12" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>94.66666666666667</v>
+        <v>96.00000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>95.55555555555557</v>
+        <v>96.44444444444446</v>
       </c>
       <c r="D13" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>94.6127946127946</v>
+        <v>95.97306397306397</v>
       </c>
       <c r="G13" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="H13" t="n">
-        <v>2.666666666666666</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="I13" t="n">
-        <v>2.222222222222219</v>
+        <v>4.838120234906054</v>
       </c>
       <c r="J13" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.333333333333333</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="L13" t="n">
-        <v>2.693602693602695</v>
+        <v>5.363652215794517</v>
       </c>
       <c r="M13" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>94.66666666666667</v>
+        <v>96.00000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>95.55555555555557</v>
+        <v>96.44444444444446</v>
       </c>
       <c r="D14" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>94.6127946127946</v>
+        <v>95.97306397306397</v>
       </c>
       <c r="G14" t="n">
-        <v>94.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="H14" t="n">
-        <v>2.666666666666666</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="I14" t="n">
-        <v>2.222222222222219</v>
+        <v>4.838120234906054</v>
       </c>
       <c r="J14" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>1.333333333333333</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="L14" t="n">
-        <v>2.693602693602695</v>
+        <v>5.363652215794517</v>
       </c>
       <c r="M14" t="n">
-        <v>2.666666666666671</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B15" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="C15" t="n">
-        <v>95.55555555555557</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="D15" t="n">
         <v>94.66666666666666</v>
@@ -1225,279 +1225,279 @@
         <v>97.33333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>94.6127946127946</v>
+        <v>94.62626262626263</v>
       </c>
       <c r="G15" t="n">
         <v>94.66666666666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2.666666666666666</v>
+        <v>4.988876515698587</v>
       </c>
       <c r="I15" t="n">
-        <v>2.222222222222219</v>
+        <v>4.521553322083512</v>
       </c>
       <c r="J15" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="K15" t="n">
-        <v>1.333333333333333</v>
+        <v>2.494438257849297</v>
       </c>
       <c r="L15" t="n">
-        <v>2.693602693602695</v>
+        <v>5.017698160896139</v>
       </c>
       <c r="M15" t="n">
-        <v>2.666666666666671</v>
+        <v>4.988876515698588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C16" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D16" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E16" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G16" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H16" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I16" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J16" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K16" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L16" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M16" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C17" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D17" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E17" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G17" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H17" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I17" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J17" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K17" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L17" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M17" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C18" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D18" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E18" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G18" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H18" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I18" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J18" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K18" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L18" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M18" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C19" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D19" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E19" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G19" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H19" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I19" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J19" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K19" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L19" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M19" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C20" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D20" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E20" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G20" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H20" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I20" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J20" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K20" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L20" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M20" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="C21" t="n">
-        <v>95.55555555555557</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="D21" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="E21" t="n">
-        <v>97.33333333333334</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>94.6127946127946</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="G21" t="n">
-        <v>94.66666666666666</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="H21" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="I21" t="n">
-        <v>2.222222222222219</v>
+        <v>2.721655269759083</v>
       </c>
       <c r="J21" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
       <c r="K21" t="n">
-        <v>1.333333333333333</v>
+        <v>1.632993161855452</v>
       </c>
       <c r="L21" t="n">
-        <v>2.693602693602695</v>
+        <v>3.29897608455647</v>
       </c>
       <c r="M21" t="n">
-        <v>2.666666666666671</v>
+        <v>3.265986323710909</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>94.66666666666667</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>94.66666666666667</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24" t="n">
         <v>94.66666666666667</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
         <v>94.66666666666667</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="n">
         <v>94.66666666666667</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
         <v>94.66666666666667</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28" t="n">
         <v>94.66666666666667</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B29" t="n">
         <v>94.66666666666667</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" t="n">
         <v>94.66666666666667</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
         <v>94.66666666666667</v>
@@ -1907,259 +1907,259 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D32" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E32" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F32" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G32" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I32" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J32" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K32" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L32" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M32" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C33" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D33" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E33" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F33" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G33" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J33" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K33" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L33" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M33" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C34" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D34" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E34" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F34" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G34" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I34" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J34" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K34" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L34" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M34" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C35" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D35" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E35" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F35" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G35" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I35" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J35" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K35" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L35" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M35" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C36" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D36" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E36" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F36" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G36" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I36" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J36" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K36" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L36" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M36" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D37" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E37" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F37" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G37" t="n">
-        <v>95.99999999999997</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3.265986323710903</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J37" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K37" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L37" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M37" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B38" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="C38" t="n">
-        <v>95.33333333333334</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D38" t="n">
         <v>94.66666666666666</v>
@@ -2168,203 +2168,203 @@
         <v>97.33333333333334</v>
       </c>
       <c r="F38" t="n">
-        <v>94.62626262626263</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G38" t="n">
         <v>94.66666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4.988876515698587</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I38" t="n">
-        <v>4.521553322083512</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J38" t="n">
-        <v>4.988876515698588</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K38" t="n">
-        <v>2.494438257849297</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L38" t="n">
-        <v>5.017698160896139</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M38" t="n">
-        <v>4.988876515698588</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C39" t="n">
-        <v>96.44444444444446</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D39" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E39" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F39" t="n">
-        <v>95.97306397306397</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G39" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5.333333333333332</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I39" t="n">
-        <v>4.838120234906054</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J39" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K39" t="n">
-        <v>2.66666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L39" t="n">
-        <v>5.363652215794517</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M39" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C40" t="n">
-        <v>96.44444444444446</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D40" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E40" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F40" t="n">
-        <v>95.97306397306397</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G40" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H40" t="n">
-        <v>5.333333333333332</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I40" t="n">
-        <v>4.838120234906054</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J40" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K40" t="n">
-        <v>2.66666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L40" t="n">
-        <v>5.363652215794517</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M40" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C41" t="n">
-        <v>96.44444444444446</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D41" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E41" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F41" t="n">
-        <v>95.97306397306397</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G41" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5.333333333333332</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I41" t="n">
-        <v>4.838120234906054</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J41" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K41" t="n">
-        <v>2.66666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L41" t="n">
-        <v>5.363652215794517</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M41" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C42" t="n">
-        <v>96.44444444444446</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E42" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F42" t="n">
-        <v>95.97306397306397</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G42" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>5.333333333333332</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I42" t="n">
-        <v>4.838120234906054</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J42" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K42" t="n">
-        <v>2.66666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L42" t="n">
-        <v>5.363652215794517</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M42" t="n">
-        <v>5.333333333333333</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B43" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="C43" t="n">
-        <v>95.33333333333334</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D43" t="n">
         <v>94.66666666666666</v>
@@ -2373,74 +2373,74 @@
         <v>97.33333333333334</v>
       </c>
       <c r="F43" t="n">
-        <v>94.62626262626263</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G43" t="n">
         <v>94.66666666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>4.988876515698587</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I43" t="n">
-        <v>4.521553322083512</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J43" t="n">
-        <v>4.988876515698588</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K43" t="n">
-        <v>2.494438257849297</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L43" t="n">
-        <v>5.017698160896139</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M43" t="n">
-        <v>4.988876515698588</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C44" t="n">
-        <v>94.22222222222223</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D44" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E44" t="n">
-        <v>96.66666666666666</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F44" t="n">
-        <v>93.27946127946127</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G44" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I44" t="n">
-        <v>3.874576838702822</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J44" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K44" t="n">
-        <v>2.108185106778923</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L44" t="n">
-        <v>4.237697115206764</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M44" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B45" t="n">
         <v>94.66666666666667</v>
@@ -2481,89 +2481,89 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C46" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D46" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E46" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F46" t="n">
-        <v>95.95959595959596</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G46" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I46" t="n">
-        <v>2.721655269759083</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J46" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K46" t="n">
-        <v>1.632993161855452</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L46" t="n">
-        <v>3.29897608455647</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M46" t="n">
-        <v>3.265986323710909</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C47" t="n">
-        <v>94.76190476190476</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D47" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E47" t="n">
-        <v>96.66666666666666</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F47" t="n">
-        <v>93.18181818181819</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G47" t="n">
-        <v>93.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H47" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I47" t="n">
-        <v>3.036686741223649</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J47" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K47" t="n">
-        <v>2.108185106778923</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L47" t="n">
-        <v>4.393262070942723</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M47" t="n">
-        <v>4.216370213557838</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B48" t="n">
         <v>94.66666666666667</v>
@@ -2604,125 +2604,84 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>90.66666666666666</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C49" t="n">
-        <v>92.85714285714286</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D49" t="n">
-        <v>90.66666666666666</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E49" t="n">
-        <v>95.33333333333334</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>90.4040404040404</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G49" t="n">
-        <v>90.66666666666666</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>1.944039478399352</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J49" t="n">
-        <v>3.265986323710897</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K49" t="n">
-        <v>1.632993161855457</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L49" t="n">
-        <v>3.505162089841245</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M49" t="n">
-        <v>3.265986323710897</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>89.33333333333333</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>92.06349206349206</v>
+        <v>95.55555555555557</v>
       </c>
       <c r="D50" t="n">
-        <v>89.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E50" t="n">
-        <v>94.66666666666667</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F50" t="n">
-        <v>88.97306397306399</v>
+        <v>94.6127946127946</v>
       </c>
       <c r="G50" t="n">
-        <v>89.33333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>1.944039478399352</v>
+        <v>2.222222222222219</v>
       </c>
       <c r="J50" t="n">
-        <v>3.265986323710897</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="K50" t="n">
-        <v>1.632993161855457</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L50" t="n">
-        <v>3.505162089841244</v>
+        <v>2.693602693602695</v>
       </c>
       <c r="M50" t="n">
-        <v>3.265986323710897</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" t="n">
-        <v>90.66666666666666</v>
-      </c>
-      <c r="C51" t="n">
-        <v>92.22222222222223</v>
-      </c>
-      <c r="D51" t="n">
-        <v>90.66666666666666</v>
-      </c>
-      <c r="E51" t="n">
-        <v>95.33333333333334</v>
-      </c>
-      <c r="F51" t="n">
-        <v>90.52188552188551</v>
-      </c>
-      <c r="G51" t="n">
-        <v>90.66666666666666</v>
-      </c>
-      <c r="H51" t="n">
-        <v>5.333333333333332</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4.444444444444446</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.333333333333332</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="L51" t="n">
-        <v>5.488215488215489</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.333333333333332</v>
+        <v>2.666666666666671</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2783,7 +2742,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -2809,7 +2768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -2835,7 +2794,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -2861,59 +2820,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>94.44444444444446</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="E5" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>96.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>93.26599326599326</v>
+        <v>79.54545454545455</v>
       </c>
       <c r="H5" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -2939,33 +2898,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>94.44444444444446</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E8" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>93.26599326599326</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H8" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -2991,59 +2950,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>94.44444444444446</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E10" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>93.26599326599326</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H10" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -3069,33 +3028,33 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>94.44444444444446</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E13" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>93.26599326599326</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H13" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -3121,59 +3080,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>94.44444444444446</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E15" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>93.26599326599326</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H15" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -3199,33 +3158,33 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
@@ -3251,7 +3210,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
@@ -3277,33 +3236,33 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
         <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -3329,33 +3288,33 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -3381,59 +3340,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D25" t="n">
-        <v>94.44444444444446</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E25" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>93.26599326599326</v>
+        <v>86.11111111111111</v>
       </c>
       <c r="H25" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -3459,59 +3418,59 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
@@ -3537,33 +3496,33 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -3589,7 +3548,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
         <v>2</v>
@@ -3615,33 +3574,33 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
@@ -3667,33 +3626,33 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
@@ -3719,7 +3678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
@@ -3745,85 +3704,85 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D39" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D40" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E40" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G40" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H40" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D41" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E41" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
@@ -3849,7 +3808,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B43" t="n">
         <v>2</v>
@@ -3875,59 +3834,59 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E44" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D45" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E45" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F45" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H45" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B46" t="n">
         <v>5</v>
@@ -3953,7 +3912,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>1</v>
@@ -3979,85 +3938,85 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E48" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
         <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D49" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E49" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F49" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E50" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F50" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H50" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
         <v>5</v>
@@ -4083,7 +4042,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
         <v>1</v>
@@ -4109,7 +4068,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
@@ -4135,59 +4094,59 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B54" t="n">
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D54" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E54" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D55" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E55" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H55" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
         <v>5</v>
@@ -4213,7 +4172,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
         <v>1</v>
@@ -4239,85 +4198,85 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D58" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E58" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E59" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E60" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F60" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G60" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H60" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B61" t="n">
         <v>5</v>
@@ -4343,7 +4302,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B62" t="n">
         <v>1</v>
@@ -4369,85 +4328,85 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D63" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E63" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B64" t="n">
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D64" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D65" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E65" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F65" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G65" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H65" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B66" t="n">
         <v>5</v>
@@ -4473,7 +4432,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B67" t="n">
         <v>1</v>
@@ -4499,7 +4458,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
@@ -4525,59 +4484,59 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D69" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E69" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H69" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D70" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E70" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G70" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H70" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B71" t="n">
         <v>5</v>
@@ -4603,7 +4562,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B72" t="n">
         <v>1</v>
@@ -4629,7 +4588,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B73" t="n">
         <v>2</v>
@@ -4655,33 +4614,33 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D74" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F74" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B75" t="n">
         <v>4</v>
@@ -4707,7 +4666,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B76" t="n">
         <v>5</v>
@@ -4733,7 +4692,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
@@ -4759,7 +4718,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
@@ -4785,33 +4744,33 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B79" t="n">
         <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D79" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E79" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H79" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B80" t="n">
         <v>4</v>
@@ -4837,7 +4796,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B81" t="n">
         <v>5</v>
@@ -4863,7 +4822,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B82" t="n">
         <v>1</v>
@@ -4889,7 +4848,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
@@ -4915,33 +4874,33 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D84" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E84" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H84" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B85" t="n">
         <v>4</v>
@@ -4967,7 +4926,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B86" t="n">
         <v>5</v>
@@ -4993,7 +4952,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B87" t="n">
         <v>1</v>
@@ -5019,7 +4978,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B88" t="n">
         <v>2</v>
@@ -5045,33 +5004,33 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B89" t="n">
         <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E89" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H89" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B90" t="n">
         <v>4</v>
@@ -5097,7 +5056,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B91" t="n">
         <v>5</v>
@@ -5123,7 +5082,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B92" t="n">
         <v>1</v>
@@ -5149,7 +5108,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B93" t="n">
         <v>2</v>
@@ -5175,33 +5134,33 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B94" t="n">
         <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D94" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E94" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F94" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
@@ -5227,7 +5186,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B96" t="n">
         <v>5</v>
@@ -5253,7 +5212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B97" t="n">
         <v>1</v>
@@ -5279,7 +5238,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B98" t="n">
         <v>2</v>
@@ -5305,33 +5264,33 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B99" t="n">
         <v>3</v>
       </c>
       <c r="C99" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E99" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F99" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G99" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H99" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B100" t="n">
         <v>4</v>
@@ -5357,7 +5316,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B101" t="n">
         <v>5</v>
@@ -5383,7 +5342,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B102" t="n">
         <v>1</v>
@@ -5409,7 +5368,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B103" t="n">
         <v>2</v>
@@ -5435,7 +5394,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B104" t="n">
         <v>3</v>
@@ -5461,7 +5420,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B105" t="n">
         <v>4</v>
@@ -5487,7 +5446,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B106" t="n">
         <v>5</v>
@@ -5513,7 +5472,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -5539,7 +5498,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B108" t="n">
         <v>2</v>
@@ -5565,7 +5524,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B109" t="n">
         <v>3</v>
@@ -5591,7 +5550,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B110" t="n">
         <v>4</v>
@@ -5617,7 +5576,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B111" t="n">
         <v>5</v>
@@ -5643,7 +5602,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B112" t="n">
         <v>1</v>
@@ -5669,7 +5628,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B113" t="n">
         <v>2</v>
@@ -5695,7 +5654,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B114" t="n">
         <v>3</v>
@@ -5721,7 +5680,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B115" t="n">
         <v>4</v>
@@ -5747,7 +5706,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B116" t="n">
         <v>5</v>
@@ -5773,7 +5732,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B117" t="n">
         <v>1</v>
@@ -5799,7 +5758,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B118" t="n">
         <v>2</v>
@@ -5825,7 +5784,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B119" t="n">
         <v>3</v>
@@ -5851,7 +5810,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B120" t="n">
         <v>4</v>
@@ -5877,7 +5836,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B121" t="n">
         <v>5</v>
@@ -5903,7 +5862,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B122" t="n">
         <v>1</v>
@@ -5929,7 +5888,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B123" t="n">
         <v>2</v>
@@ -5955,7 +5914,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B124" t="n">
         <v>3</v>
@@ -5981,7 +5940,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B125" t="n">
         <v>4</v>
@@ -6007,7 +5966,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B126" t="n">
         <v>5</v>
@@ -6033,7 +5992,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B127" t="n">
         <v>1</v>
@@ -6059,7 +6018,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B128" t="n">
         <v>2</v>
@@ -6085,7 +6044,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B129" t="n">
         <v>3</v>
@@ -6111,7 +6070,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B130" t="n">
         <v>4</v>
@@ -6137,7 +6096,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B131" t="n">
         <v>5</v>
@@ -6163,7 +6122,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B132" t="n">
         <v>1</v>
@@ -6189,7 +6148,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B133" t="n">
         <v>2</v>
@@ -6215,7 +6174,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B134" t="n">
         <v>3</v>
@@ -6241,7 +6200,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B135" t="n">
         <v>4</v>
@@ -6267,7 +6226,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B136" t="n">
         <v>5</v>
@@ -6293,7 +6252,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B137" t="n">
         <v>1</v>
@@ -6319,7 +6278,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B138" t="n">
         <v>2</v>
@@ -6345,7 +6304,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B139" t="n">
         <v>3</v>
@@ -6371,7 +6330,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B140" t="n">
         <v>4</v>
@@ -6397,7 +6356,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B141" t="n">
         <v>5</v>
@@ -6423,7 +6382,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B142" t="n">
         <v>1</v>
@@ -6449,7 +6408,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B143" t="n">
         <v>2</v>
@@ -6475,7 +6434,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B144" t="n">
         <v>3</v>
@@ -6501,7 +6460,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B145" t="n">
         <v>4</v>
@@ -6527,7 +6486,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B146" t="n">
         <v>5</v>
@@ -6553,7 +6512,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B147" t="n">
         <v>1</v>
@@ -6579,7 +6538,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B148" t="n">
         <v>2</v>
@@ -6605,7 +6564,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B149" t="n">
         <v>3</v>
@@ -6631,7 +6590,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B150" t="n">
         <v>4</v>
@@ -6657,7 +6616,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B151" t="n">
         <v>5</v>
@@ -6683,7 +6642,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B152" t="n">
         <v>1</v>
@@ -6709,7 +6668,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B153" t="n">
         <v>2</v>
@@ -6735,33 +6694,33 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B154" t="n">
         <v>3</v>
       </c>
       <c r="C154" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D154" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E154" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F154" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G154" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H154" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B155" t="n">
         <v>4</v>
@@ -6787,7 +6746,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B156" t="n">
         <v>5</v>
@@ -6813,7 +6772,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B157" t="n">
         <v>1</v>
@@ -6839,7 +6798,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B158" t="n">
         <v>2</v>
@@ -6865,33 +6824,33 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B159" t="n">
         <v>3</v>
       </c>
       <c r="C159" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D159" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E159" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F159" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G159" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H159" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B160" t="n">
         <v>4</v>
@@ -6917,7 +6876,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B161" t="n">
         <v>5</v>
@@ -6943,7 +6902,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B162" t="n">
         <v>1</v>
@@ -6969,7 +6928,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B163" t="n">
         <v>2</v>
@@ -6995,33 +6954,33 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B164" t="n">
         <v>3</v>
       </c>
       <c r="C164" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D164" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E164" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F164" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G164" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H164" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B165" t="n">
         <v>4</v>
@@ -7047,7 +7006,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B166" t="n">
         <v>5</v>
@@ -7073,7 +7032,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B167" t="n">
         <v>1</v>
@@ -7099,7 +7058,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B168" t="n">
         <v>2</v>
@@ -7125,33 +7084,33 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B169" t="n">
         <v>3</v>
       </c>
       <c r="C169" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D169" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E169" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F169" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G169" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H169" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B170" t="n">
         <v>4</v>
@@ -7177,7 +7136,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B171" t="n">
         <v>5</v>
@@ -7203,7 +7162,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B172" t="n">
         <v>1</v>
@@ -7229,7 +7188,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B173" t="n">
         <v>2</v>
@@ -7255,33 +7214,33 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B174" t="n">
         <v>3</v>
       </c>
       <c r="C174" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D174" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E174" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F174" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G174" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H174" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B175" t="n">
         <v>4</v>
@@ -7307,7 +7266,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B176" t="n">
         <v>5</v>
@@ -7333,7 +7292,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B177" t="n">
         <v>1</v>
@@ -7359,7 +7318,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B178" t="n">
         <v>2</v>
@@ -7385,33 +7344,33 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B179" t="n">
         <v>3</v>
       </c>
       <c r="C179" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D179" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E179" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F179" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G179" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H179" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B180" t="n">
         <v>4</v>
@@ -7437,7 +7396,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B181" t="n">
         <v>5</v>
@@ -7463,7 +7422,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B182" t="n">
         <v>1</v>
@@ -7489,7 +7448,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B183" t="n">
         <v>2</v>
@@ -7515,59 +7474,59 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B184" t="n">
         <v>3</v>
       </c>
       <c r="C184" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D184" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E184" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F184" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G184" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H184" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B185" t="n">
         <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D185" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E185" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F185" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G185" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H185" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B186" t="n">
         <v>5</v>
@@ -7593,7 +7552,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B187" t="n">
         <v>1</v>
@@ -7619,85 +7578,85 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B188" t="n">
         <v>2</v>
       </c>
       <c r="C188" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D188" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E188" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F188" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G188" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H188" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B189" t="n">
         <v>3</v>
       </c>
       <c r="C189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D189" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F189" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G189" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B190" t="n">
         <v>4</v>
       </c>
       <c r="C190" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D190" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E190" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F190" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G190" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H190" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B191" t="n">
         <v>5</v>
@@ -7723,7 +7682,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B192" t="n">
         <v>1</v>
@@ -7749,85 +7708,85 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B193" t="n">
         <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D193" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E193" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F193" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G193" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H193" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B194" t="n">
         <v>3</v>
       </c>
       <c r="C194" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D194" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E194" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F194" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G194" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H194" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B195" t="n">
         <v>4</v>
       </c>
       <c r="C195" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D195" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E195" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F195" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G195" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H195" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B196" t="n">
         <v>5</v>
@@ -7853,7 +7812,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B197" t="n">
         <v>1</v>
@@ -7879,85 +7838,85 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B198" t="n">
         <v>2</v>
       </c>
       <c r="C198" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D198" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E198" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F198" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G198" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H198" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B199" t="n">
         <v>3</v>
       </c>
       <c r="C199" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D199" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E199" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F199" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G199" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H199" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B200" t="n">
         <v>4</v>
       </c>
       <c r="C200" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D200" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E200" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F200" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G200" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H200" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B201" t="n">
         <v>5</v>
@@ -7983,7 +7942,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B202" t="n">
         <v>1</v>
@@ -8009,85 +7968,85 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B203" t="n">
         <v>2</v>
       </c>
       <c r="C203" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D203" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E203" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F203" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G203" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H203" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B204" t="n">
         <v>3</v>
       </c>
       <c r="C204" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D204" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E204" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F204" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G204" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H204" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B205" t="n">
         <v>4</v>
       </c>
       <c r="C205" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D205" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E205" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F205" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G205" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H205" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B206" t="n">
         <v>5</v>
@@ -8113,7 +8072,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B207" t="n">
         <v>1</v>
@@ -8139,7 +8098,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B208" t="n">
         <v>2</v>
@@ -8165,59 +8124,59 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B209" t="n">
         <v>3</v>
       </c>
       <c r="C209" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D209" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E209" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F209" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G209" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H209" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B210" t="n">
         <v>4</v>
       </c>
       <c r="C210" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D210" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E210" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F210" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G210" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H210" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B211" t="n">
         <v>5</v>
@@ -8243,7 +8202,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B212" t="n">
         <v>1</v>
@@ -8269,7 +8228,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B213" t="n">
         <v>2</v>
@@ -8295,85 +8254,85 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B214" t="n">
         <v>3</v>
       </c>
       <c r="C214" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D214" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E214" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F214" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G214" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H214" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B215" t="n">
         <v>4</v>
       </c>
       <c r="C215" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D215" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E215" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F215" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G215" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H215" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B216" t="n">
         <v>5</v>
       </c>
       <c r="C216" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D216" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E216" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F216" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G216" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H216" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B217" t="n">
         <v>1</v>
@@ -8399,7 +8358,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B218" t="n">
         <v>2</v>
@@ -8425,33 +8384,33 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B219" t="n">
         <v>3</v>
       </c>
       <c r="C219" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D219" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E219" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F219" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G219" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H219" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B220" t="n">
         <v>4</v>
@@ -8477,33 +8436,33 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B221" t="n">
         <v>5</v>
       </c>
       <c r="C221" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D221" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E221" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F221" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G221" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H221" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B222" t="n">
         <v>1</v>
@@ -8529,59 +8488,59 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B223" t="n">
         <v>2</v>
       </c>
       <c r="C223" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D223" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E223" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F223" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G223" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H223" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B224" t="n">
         <v>3</v>
       </c>
       <c r="C224" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D224" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E224" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F224" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G224" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H224" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B225" t="n">
         <v>4</v>
@@ -8607,33 +8566,33 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B226" t="n">
         <v>5</v>
       </c>
       <c r="C226" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D226" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E226" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F226" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G226" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H226" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B227" t="n">
         <v>1</v>
@@ -8659,33 +8618,33 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B228" t="n">
         <v>2</v>
       </c>
       <c r="C228" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D228" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E228" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F228" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G228" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H228" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B229" t="n">
         <v>3</v>
@@ -8711,59 +8670,59 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B230" t="n">
         <v>4</v>
       </c>
       <c r="C230" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D230" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E230" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F230" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G230" t="n">
-        <v>86.11111111111111</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H230" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B231" t="n">
         <v>5</v>
       </c>
       <c r="C231" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D231" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E231" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F231" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G231" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H231" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B232" t="n">
         <v>1</v>
@@ -8789,33 +8748,33 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B233" t="n">
         <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D233" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E233" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F233" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G233" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H233" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B234" t="n">
         <v>3</v>
@@ -8841,7 +8800,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B235" t="n">
         <v>4</v>
@@ -8867,33 +8826,33 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B236" t="n">
         <v>5</v>
       </c>
       <c r="C236" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D236" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E236" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F236" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G236" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H236" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B237" t="n">
         <v>1</v>
@@ -8919,33 +8878,33 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B238" t="n">
         <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D238" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E238" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F238" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G238" t="n">
-        <v>86.11111111111111</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H238" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B239" t="n">
         <v>3</v>
@@ -8971,59 +8930,59 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B240" t="n">
         <v>4</v>
       </c>
       <c r="C240" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D240" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E240" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F240" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G240" t="n">
-        <v>86.11111111111111</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H240" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B241" t="n">
         <v>5</v>
       </c>
       <c r="C241" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D241" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E241" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F241" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G241" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H241" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B242" t="n">
         <v>1</v>
@@ -9049,33 +9008,33 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B243" t="n">
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D243" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E243" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F243" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G243" t="n">
-        <v>86.11111111111111</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H243" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B244" t="n">
         <v>3</v>
@@ -9101,184 +9060,54 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B245" t="n">
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D245" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E245" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F245" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G245" t="n">
-        <v>86.11111111111111</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H245" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B246" t="n">
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>86.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="D246" t="n">
-        <v>90.47619047619048</v>
+        <v>100</v>
       </c>
       <c r="E246" t="n">
-        <v>86.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="F246" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="G246" t="n">
-        <v>86.11111111111111</v>
+        <v>100</v>
       </c>
       <c r="H246" t="n">
-        <v>86.66666666666667</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>1</v>
-      </c>
-      <c r="B247" t="n">
-        <v>1</v>
-      </c>
-      <c r="C247" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="D247" t="n">
-        <v>94.44444444444446</v>
-      </c>
-      <c r="E247" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F247" t="n">
-        <v>96.66666666666667</v>
-      </c>
-      <c r="G247" t="n">
-        <v>93.26599326599326</v>
-      </c>
-      <c r="H247" t="n">
-        <v>93.33333333333333</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>1</v>
-      </c>
-      <c r="B248" t="n">
-        <v>2</v>
-      </c>
-      <c r="C248" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="D248" t="n">
-        <v>94.44444444444446</v>
-      </c>
-      <c r="E248" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F248" t="n">
-        <v>96.66666666666667</v>
-      </c>
-      <c r="G248" t="n">
-        <v>93.26599326599326</v>
-      </c>
-      <c r="H248" t="n">
-        <v>93.33333333333333</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>1</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3</v>
-      </c>
-      <c r="C249" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="D249" t="n">
-        <v>94.44444444444446</v>
-      </c>
-      <c r="E249" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F249" t="n">
-        <v>96.66666666666667</v>
-      </c>
-      <c r="G249" t="n">
-        <v>93.26599326599326</v>
-      </c>
-      <c r="H249" t="n">
-        <v>93.33333333333333</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>1</v>
-      </c>
-      <c r="B250" t="n">
-        <v>4</v>
-      </c>
-      <c r="C250" t="n">
-        <v>80</v>
-      </c>
-      <c r="D250" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="E250" t="n">
-        <v>80</v>
-      </c>
-      <c r="F250" t="n">
-        <v>90</v>
-      </c>
-      <c r="G250" t="n">
-        <v>79.54545454545455</v>
-      </c>
-      <c r="H250" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>1</v>
-      </c>
-      <c r="B251" t="n">
-        <v>5</v>
-      </c>
-      <c r="C251" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="D251" t="n">
-        <v>94.44444444444446</v>
-      </c>
-      <c r="E251" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F251" t="n">
-        <v>96.66666666666667</v>
-      </c>
-      <c r="G251" t="n">
-        <v>93.26599326599326</v>
-      </c>
-      <c r="H251" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -9319,7 +9148,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>95.97306397306397</v>
@@ -9332,7 +9161,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>96.00000000000001</v>
@@ -9345,7 +9174,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>

--- a/Results/Stand/Normal/FindPrincipalComponents_PipelinePCA_Stand/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Stand/Normal/FindPrincipalComponents_PipelinePCA_Stand/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,10 +585,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Show Accuracy Threshold</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accuracy Threshold (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Highlight Acceptable Accuracy</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Master Path</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>/Users/mohammad/University/Bachelor Project/Final/Data/Stand/Master Features/MASTER_Features_Stand.xlsx</t>
         </is>
@@ -1049,40 +1079,40 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>96.00000000000001</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="C11" t="n">
-        <v>96.44444444444446</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="E11" t="n">
-        <v>98.00000000000001</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>95.97306397306397</v>
+        <v>94.62626262626263</v>
       </c>
       <c r="G11" t="n">
-        <v>96</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H11" t="n">
-        <v>5.333333333333332</v>
+        <v>4.988876515698587</v>
       </c>
       <c r="I11" t="n">
-        <v>4.838120234906054</v>
+        <v>4.521553322083512</v>
       </c>
       <c r="J11" t="n">
-        <v>5.333333333333333</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="K11" t="n">
-        <v>2.66666666666667</v>
+        <v>2.494438257849297</v>
       </c>
       <c r="L11" t="n">
-        <v>5.363652215794517</v>
+        <v>5.017698160896139</v>
       </c>
       <c r="M11" t="n">
-        <v>5.333333333333333</v>
+        <v>4.988876515698588</v>
       </c>
     </row>
     <row r="12">
@@ -3944,22 +3974,22 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -9148,7 +9178,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>95.97306397306397</v>
